--- a/reports/Debug-snowbowl-20251216/For The Day (Actual)_Payroll.xlsx
+++ b/reports/Debug-snowbowl-20251216/For The Day (Actual)_Payroll.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="233">
   <si>
     <t>eecode</t>
   </si>
@@ -46,108 +46,108 @@
     <t>DepartmentTitle</t>
   </si>
   <si>
+    <t>F058</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>OD</t>
+  </si>
+  <si>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>Lift Operations</t>
+  </si>
+  <si>
+    <t>A2CL</t>
+  </si>
+  <si>
+    <t>A3ML</t>
+  </si>
+  <si>
+    <t>F627</t>
+  </si>
+  <si>
+    <t>H352</t>
+  </si>
+  <si>
+    <t>G961</t>
+  </si>
+  <si>
+    <t>A0OV</t>
+  </si>
+  <si>
+    <t>D816</t>
+  </si>
+  <si>
+    <t>E483</t>
+  </si>
+  <si>
+    <t>D954</t>
+  </si>
+  <si>
+    <t>C791</t>
+  </si>
+  <si>
+    <t>B884</t>
+  </si>
+  <si>
+    <t>A749</t>
+  </si>
+  <si>
+    <t>A4BY</t>
+  </si>
+  <si>
+    <t>A3SS</t>
+  </si>
+  <si>
+    <t>A3OA</t>
+  </si>
+  <si>
+    <t>J405</t>
+  </si>
+  <si>
+    <t>A2C7</t>
+  </si>
+  <si>
+    <t>A2BR</t>
+  </si>
+  <si>
+    <t>A0BA</t>
+  </si>
+  <si>
+    <t>A3R8</t>
+  </si>
+  <si>
+    <t>H632</t>
+  </si>
+  <si>
+    <t>A31F</t>
+  </si>
+  <si>
     <t>A3MX</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>OD</t>
-  </si>
-  <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>Lift Operations</t>
-  </si>
-  <si>
-    <t>A3R8</t>
-  </si>
-  <si>
     <t>D521</t>
   </si>
   <si>
-    <t>A0BA</t>
+    <t>C346</t>
+  </si>
+  <si>
+    <t>C282</t>
+  </si>
+  <si>
+    <t>A3OF</t>
+  </si>
+  <si>
+    <t>A3MY</t>
   </si>
   <si>
     <t>B202</t>
   </si>
   <si>
-    <t>A3OA</t>
-  </si>
-  <si>
-    <t>A3SS</t>
-  </si>
-  <si>
-    <t>A4BY</t>
-  </si>
-  <si>
-    <t>H632</t>
-  </si>
-  <si>
-    <t>A749</t>
-  </si>
-  <si>
-    <t>B884</t>
-  </si>
-  <si>
-    <t>F627</t>
-  </si>
-  <si>
-    <t>A3ML</t>
-  </si>
-  <si>
-    <t>A2CL</t>
-  </si>
-  <si>
-    <t>H352</t>
-  </si>
-  <si>
-    <t>G961</t>
-  </si>
-  <si>
-    <t>E483</t>
-  </si>
-  <si>
-    <t>C282</t>
-  </si>
-  <si>
-    <t>A31F</t>
-  </si>
-  <si>
-    <t>A3MY</t>
-  </si>
-  <si>
-    <t>A3OF</t>
-  </si>
-  <si>
-    <t>F058</t>
-  </si>
-  <si>
-    <t>D954</t>
-  </si>
-  <si>
-    <t>A2C7</t>
-  </si>
-  <si>
-    <t>D816</t>
-  </si>
-  <si>
-    <t>A0OV</t>
-  </si>
-  <si>
-    <t>J405</t>
-  </si>
-  <si>
-    <t>C346</t>
-  </si>
-  <si>
-    <t>A2BR</t>
-  </si>
-  <si>
-    <t>C791</t>
-  </si>
-  <si>
     <t>B221</t>
   </si>
   <si>
@@ -157,54 +157,54 @@
     <t>Lift Maintenance</t>
   </si>
   <si>
+    <t>A3I8</t>
+  </si>
+  <si>
     <t>A3J5</t>
   </si>
   <si>
-    <t>A3I8</t>
+    <t>A3IS</t>
+  </si>
+  <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>Snowmaking</t>
+  </si>
+  <si>
+    <t>A0QH</t>
+  </si>
+  <si>
+    <t>E568</t>
   </si>
   <si>
     <t>A3J1</t>
   </si>
   <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>Snowmaking</t>
-  </si>
-  <si>
-    <t>E568</t>
-  </si>
-  <si>
-    <t>A3IS</t>
+    <t>A3IC</t>
+  </si>
+  <si>
+    <t>A3LD</t>
   </si>
   <si>
     <t>A3IA</t>
   </si>
   <si>
-    <t>A3LD</t>
-  </si>
-  <si>
-    <t>A0QH</t>
-  </si>
-  <si>
-    <t>A3IC</t>
+    <t>F497</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>Terrain Park</t>
+  </si>
+  <si>
+    <t>A10D</t>
   </si>
   <si>
     <t>F703</t>
   </si>
   <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>Terrain Park</t>
-  </si>
-  <si>
-    <t>F497</t>
-  </si>
-  <si>
-    <t>A10D</t>
-  </si>
-  <si>
     <t>C215</t>
   </si>
   <si>
@@ -232,141 +232,141 @@
     <t>Vehicle Maintenance</t>
   </si>
   <si>
+    <t>G190</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>Ski Patrol</t>
+  </si>
+  <si>
+    <t>G573</t>
+  </si>
+  <si>
+    <t>H115</t>
+  </si>
+  <si>
+    <t>A278</t>
+  </si>
+  <si>
+    <t>J289</t>
+  </si>
+  <si>
+    <t>D619</t>
+  </si>
+  <si>
+    <t>A3HZ</t>
+  </si>
+  <si>
+    <t>D172</t>
+  </si>
+  <si>
+    <t>A3JT</t>
+  </si>
+  <si>
+    <t>I588</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
     <t>F013</t>
   </si>
   <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>Ski Patrol</t>
-  </si>
-  <si>
-    <t>D172</t>
-  </si>
-  <si>
-    <t>H115</t>
-  </si>
-  <si>
-    <t>J289</t>
-  </si>
-  <si>
-    <t>D619</t>
-  </si>
-  <si>
-    <t>A278</t>
-  </si>
-  <si>
     <t>G710</t>
   </si>
   <si>
-    <t>A3HZ</t>
-  </si>
-  <si>
-    <t>G573</t>
-  </si>
-  <si>
-    <t>G190</t>
-  </si>
-  <si>
     <t>D576</t>
   </si>
   <si>
-    <t>A3JT</t>
-  </si>
-  <si>
-    <t>I588</t>
-  </si>
-  <si>
-    <t>HR</t>
+    <t>A2CR</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>Tickets</t>
+  </si>
+  <si>
+    <t>F510</t>
+  </si>
+  <si>
+    <t>F959</t>
+  </si>
+  <si>
+    <t>A3RQ</t>
+  </si>
+  <si>
+    <t>A2FB</t>
   </si>
   <si>
     <t>A3RR</t>
   </si>
   <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>Tickets</t>
-  </si>
-  <si>
-    <t>A2CR</t>
+    <t>A3TE</t>
   </si>
   <si>
     <t>A0QI</t>
   </si>
   <si>
-    <t>A2FB</t>
-  </si>
-  <si>
-    <t>F959</t>
-  </si>
-  <si>
-    <t>A3TE</t>
-  </si>
-  <si>
-    <t>F510</t>
-  </si>
-  <si>
-    <t>A3RQ</t>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>Ski School</t>
+  </si>
+  <si>
+    <t>G730</t>
   </si>
   <si>
     <t>A399</t>
   </si>
   <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>Ski School</t>
-  </si>
-  <si>
-    <t>G730</t>
-  </si>
-  <si>
-    <t>E190</t>
+    <t>A3RK</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>Rentals</t>
+  </si>
+  <si>
+    <t>A2YQ</t>
+  </si>
+  <si>
+    <t>A0RX</t>
+  </si>
+  <si>
+    <t>A46N</t>
+  </si>
+  <si>
+    <t>A11F</t>
+  </si>
+  <si>
+    <t>A2PL</t>
+  </si>
+  <si>
+    <t>H439</t>
+  </si>
+  <si>
+    <t>A2ID</t>
+  </si>
+  <si>
+    <t>D259</t>
   </si>
   <si>
     <t>A3LK</t>
   </si>
   <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>Rentals</t>
+    <t>A2JE</t>
   </si>
   <si>
     <t>A2I3</t>
   </si>
   <si>
-    <t>A11F</t>
-  </si>
-  <si>
-    <t>A2YQ</t>
-  </si>
-  <si>
-    <t>A3RK</t>
-  </si>
-  <si>
-    <t>D259</t>
-  </si>
-  <si>
-    <t>A2ID</t>
-  </si>
-  <si>
-    <t>A2JE</t>
-  </si>
-  <si>
-    <t>A2PL</t>
-  </si>
-  <si>
-    <t>A0RX</t>
-  </si>
-  <si>
-    <t>A46N</t>
-  </si>
-  <si>
-    <t>H439</t>
-  </si>
-  <si>
     <t>F370</t>
   </si>
   <si>
@@ -388,21 +388,21 @@
     <t>Agassiz Retail</t>
   </si>
   <si>
+    <t>A2LG</t>
+  </si>
+  <si>
+    <t>D4032</t>
+  </si>
+  <si>
+    <t>Hart Prairie Retail</t>
+  </si>
+  <si>
     <t>A3NB</t>
   </si>
   <si>
-    <t>D4032</t>
-  </si>
-  <si>
-    <t>Hart Prairie Retail</t>
-  </si>
-  <si>
     <t>B622</t>
   </si>
   <si>
-    <t>A2LG</t>
-  </si>
-  <si>
     <t>G605</t>
   </si>
   <si>
@@ -421,108 +421,108 @@
     <t>Agassiz Restaurant</t>
   </si>
   <si>
+    <t>A0H4</t>
+  </si>
+  <si>
     <t>A2KU</t>
   </si>
   <si>
+    <t>E794</t>
+  </si>
+  <si>
+    <t>A3NK</t>
+  </si>
+  <si>
+    <t>A3ZD</t>
+  </si>
+  <si>
+    <t>A3JQ</t>
+  </si>
+  <si>
+    <t>A3YI</t>
+  </si>
+  <si>
     <t>A0TT</t>
   </si>
   <si>
-    <t>A0H4</t>
+    <t>I133</t>
   </si>
   <si>
     <t>A0GT</t>
   </si>
   <si>
-    <t>E794</t>
-  </si>
-  <si>
-    <t>A3NK</t>
-  </si>
-  <si>
-    <t>A3ZD</t>
-  </si>
-  <si>
-    <t>A3JQ</t>
-  </si>
-  <si>
-    <t>I133</t>
-  </si>
-  <si>
-    <t>A3YI</t>
+    <t>A3YQ</t>
+  </si>
+  <si>
+    <t>D5111</t>
+  </si>
+  <si>
+    <t>Hart Prairie Restaurant</t>
+  </si>
+  <si>
+    <t>A3TV</t>
+  </si>
+  <si>
+    <t>A3ZB</t>
+  </si>
+  <si>
+    <t>F766</t>
+  </si>
+  <si>
+    <t>H636</t>
+  </si>
+  <si>
+    <t>A3GV</t>
+  </si>
+  <si>
+    <t>A3I6</t>
+  </si>
+  <si>
+    <t>A2K2</t>
+  </si>
+  <si>
+    <t>A2KF</t>
+  </si>
+  <si>
+    <t>A3UE</t>
+  </si>
+  <si>
+    <t>A41E</t>
+  </si>
+  <si>
+    <t>A0VA</t>
+  </si>
+  <si>
+    <t>A3YO</t>
+  </si>
+  <si>
+    <t>A0G6</t>
+  </si>
+  <si>
+    <t>A0GJ</t>
+  </si>
+  <si>
+    <t>C926</t>
+  </si>
+  <si>
+    <t>A1H9</t>
+  </si>
+  <si>
+    <t>A45O</t>
+  </si>
+  <si>
+    <t>A0LX</t>
+  </si>
+  <si>
+    <t>A3Z9</t>
+  </si>
+  <si>
+    <t>B2UZ</t>
   </si>
   <si>
     <t>A2JX</t>
   </si>
   <si>
-    <t>D5111</t>
-  </si>
-  <si>
-    <t>Hart Prairie Restaurant</t>
-  </si>
-  <si>
-    <t>C926</t>
-  </si>
-  <si>
-    <t>A3YO</t>
-  </si>
-  <si>
-    <t>A2K2</t>
-  </si>
-  <si>
-    <t>B2UZ</t>
-  </si>
-  <si>
-    <t>A2KF</t>
-  </si>
-  <si>
-    <t>A3UE</t>
-  </si>
-  <si>
-    <t>A41E</t>
-  </si>
-  <si>
-    <t>A3YQ</t>
-  </si>
-  <si>
-    <t>A0GJ</t>
-  </si>
-  <si>
-    <t>A3ZB</t>
-  </si>
-  <si>
-    <t>F766</t>
-  </si>
-  <si>
-    <t>A3TV</t>
-  </si>
-  <si>
-    <t>A0G6</t>
-  </si>
-  <si>
-    <t>A0VA</t>
-  </si>
-  <si>
-    <t>A3I6</t>
-  </si>
-  <si>
-    <t>A3GV</t>
-  </si>
-  <si>
-    <t>A3Z9</t>
-  </si>
-  <si>
-    <t>A0LX</t>
-  </si>
-  <si>
-    <t>A45O</t>
-  </si>
-  <si>
-    <t>A1H9</t>
-  </si>
-  <si>
-    <t>H636</t>
-  </si>
-  <si>
     <t>C213</t>
   </si>
   <si>
@@ -535,57 +535,57 @@
     <t>A04Q</t>
   </si>
   <si>
+    <t>A3Z2</t>
+  </si>
+  <si>
+    <t>D5113</t>
+  </si>
+  <si>
+    <t>Fremont Restaurant</t>
+  </si>
+  <si>
+    <t>A515</t>
+  </si>
+  <si>
+    <t>A3YM</t>
+  </si>
+  <si>
     <t>A0G7</t>
   </si>
   <si>
-    <t>D5113</t>
-  </si>
-  <si>
-    <t>Fremont Restaurant</t>
-  </si>
-  <si>
-    <t>A515</t>
-  </si>
-  <si>
-    <t>A3Z2</t>
-  </si>
-  <si>
-    <t>A3YM</t>
+    <t>A2HX</t>
+  </si>
+  <si>
+    <t>D6030</t>
+  </si>
+  <si>
+    <t>Base Camp Hotel</t>
   </si>
   <si>
     <t>A3HE</t>
   </si>
   <si>
-    <t>D6030</t>
-  </si>
-  <si>
-    <t>Base Camp Hotel</t>
-  </si>
-  <si>
-    <t>A2HX</t>
-  </si>
-  <si>
     <t>E926</t>
   </si>
   <si>
+    <t>A4CZ</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>A0J5</t>
+  </si>
+  <si>
     <t>A194</t>
   </si>
   <si>
-    <t>D6215</t>
-  </si>
-  <si>
-    <t>Housekeeping</t>
-  </si>
-  <si>
-    <t>A0J5</t>
-  </si>
-  <si>
     <t>A3OR</t>
   </si>
   <si>
-    <t>A4CZ</t>
-  </si>
-  <si>
     <t>A2IA</t>
   </si>
   <si>
@@ -595,18 +595,18 @@
     <t>Parking</t>
   </si>
   <si>
+    <t>A0BO</t>
+  </si>
+  <si>
+    <t>A4AF</t>
+  </si>
+  <si>
+    <t>A37Y</t>
+  </si>
+  <si>
     <t>A4AL</t>
   </si>
   <si>
-    <t>A4AF</t>
-  </si>
-  <si>
-    <t>A37Y</t>
-  </si>
-  <si>
-    <t>A0BO</t>
-  </si>
-  <si>
     <t>A2V1</t>
   </si>
   <si>
@@ -616,42 +616,42 @@
     <t>Security</t>
   </si>
   <si>
+    <t>A2FQ</t>
+  </si>
+  <si>
+    <t>D6740</t>
+  </si>
+  <si>
+    <t>Janitorial</t>
+  </si>
+  <si>
     <t>A3TG</t>
   </si>
   <si>
-    <t>D6740</t>
-  </si>
-  <si>
-    <t>Janitorial</t>
+    <t>C947</t>
   </si>
   <si>
     <t>A2GD</t>
   </si>
   <si>
-    <t>A2FQ</t>
-  </si>
-  <si>
-    <t>C947</t>
+    <t>A3O6</t>
+  </si>
+  <si>
+    <t>D6760</t>
+  </si>
+  <si>
+    <t>Facilities Maintenance</t>
+  </si>
+  <si>
+    <t>H146</t>
   </si>
   <si>
     <t>D754</t>
   </si>
   <si>
-    <t>D6760</t>
-  </si>
-  <si>
-    <t>Facilities Maintenance</t>
-  </si>
-  <si>
-    <t>A3O6</t>
-  </si>
-  <si>
     <t>A0IJ</t>
   </si>
   <si>
-    <t>H146</t>
-  </si>
-  <si>
     <t>H577</t>
   </si>
   <si>
@@ -661,12 +661,12 @@
     <t>Grounds Maintenance</t>
   </si>
   <si>
+    <t>A3TX</t>
+  </si>
+  <si>
     <t>A3TY</t>
   </si>
   <si>
-    <t>A3TX</t>
-  </si>
-  <si>
     <t>A2PQ</t>
   </si>
   <si>
@@ -706,13 +706,13 @@
     <t>D8040</t>
   </si>
   <si>
+    <t>D9008</t>
+  </si>
+  <si>
+    <t>Capital Project 9</t>
+  </si>
+  <si>
     <t>E835</t>
-  </si>
-  <si>
-    <t>D9008</t>
-  </si>
-  <si>
-    <t>Capital Project 9</t>
   </si>
 </sst>
 </file>
@@ -1126,13 +1126,13 @@
         <v>10</v>
       </c>
       <c r="B2" s="2">
-        <v>46007.33094907407</v>
+        <v>46007.32207175926</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="2">
-        <v>46007.68743055555</v>
+        <v>46007.71020833333</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>12</v>
@@ -1141,7 +1141,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="2">
-        <v>18.35</v>
+        <v>20.7</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -1158,13 +1158,13 @@
         <v>15</v>
       </c>
       <c r="B3" s="2">
-        <v>46007.32734953704</v>
+        <v>46007.32942129629</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="2">
-        <v>46007.68322916667</v>
+        <v>46007.69011574074</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>12</v>
@@ -1173,7 +1173,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
@@ -1190,13 +1190,13 @@
         <v>16</v>
       </c>
       <c r="B4" s="2">
-        <v>46007.32733796296</v>
+        <v>46007.32349537037</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="2">
-        <v>46007.68481481481</v>
+        <v>46007.68577546296</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>12</v>
@@ -1222,13 +1222,13 @@
         <v>17</v>
       </c>
       <c r="B5" s="2">
-        <v>46007.32784722222</v>
+        <v>46007.32453703704</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="2">
-        <v>46007.68414351852</v>
+        <v>46007.69791666666</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>12</v>
@@ -1254,13 +1254,13 @@
         <v>18</v>
       </c>
       <c r="B6" s="2">
-        <v>46007.33141203703</v>
+        <v>46007.32229166666</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="2">
-        <v>46007.70413194445</v>
+        <v>46007.69791666666</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -1269,7 +1269,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="2">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -1286,13 +1286,13 @@
         <v>19</v>
       </c>
       <c r="B7" s="2">
-        <v>46007.35024305555</v>
+        <v>46007.32863425926</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="2">
-        <v>46007.70887731481</v>
+        <v>46007.6925462963</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>12</v>
@@ -1301,7 +1301,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="2">
-        <v>18.35</v>
+        <v>19.6</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -1318,13 +1318,13 @@
         <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>46007.32409722222</v>
+        <v>46007.34350694445</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="2">
-        <v>46007.70688657407</v>
+        <v>46007.68429398148</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
@@ -1333,7 +1333,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -1350,13 +1350,13 @@
         <v>21</v>
       </c>
       <c r="B9" s="2">
-        <v>46007.33047453704</v>
+        <v>46007.33208333333</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="2">
-        <v>46007.6875</v>
+        <v>46007.69263888889</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>12</v>
@@ -1365,7 +1365,7 @@
         <v>13</v>
       </c>
       <c r="G9" s="2">
-        <v>18.35</v>
+        <v>19.6</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
@@ -1382,13 +1382,13 @@
         <v>22</v>
       </c>
       <c r="B10" s="2">
-        <v>46007.27841435185</v>
+        <v>46007.32585648148</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="2">
-        <v>46007.73622685186</v>
+        <v>46007.69454861111</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>12</v>
@@ -1397,7 +1397,7 @@
         <v>13</v>
       </c>
       <c r="G10" s="2">
-        <v>26.8</v>
+        <v>18.35</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
@@ -1414,13 +1414,13 @@
         <v>23</v>
       </c>
       <c r="B11" s="2">
-        <v>46007.32270833333</v>
+        <v>46007.32291666666</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="2">
-        <v>46007.68324074074</v>
+        <v>46007.69791666666</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>12</v>
@@ -1429,7 +1429,7 @@
         <v>13</v>
       </c>
       <c r="G11" s="2">
-        <v>18.35</v>
+        <v>19.6</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -1446,13 +1446,13 @@
         <v>24</v>
       </c>
       <c r="B12" s="2">
-        <v>46007.32917824074</v>
+        <v>46007.33370370371</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="2">
-        <v>46007.70486111111</v>
+        <v>46007.625</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>12</v>
@@ -1461,7 +1461,7 @@
         <v>13</v>
       </c>
       <c r="G12" s="2">
-        <v>18.7</v>
+        <v>20.95</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -1478,13 +1478,13 @@
         <v>25</v>
       </c>
       <c r="B13" s="2">
-        <v>46007.32453703704</v>
+        <v>46007.32917824074</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="2">
-        <v>46007.69791666666</v>
+        <v>46007.70486111111</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>12</v>
@@ -1510,13 +1510,13 @@
         <v>26</v>
       </c>
       <c r="B14" s="2">
-        <v>46007.32349537037</v>
+        <v>46007.32270833333</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="2">
-        <v>46007.68577546296</v>
+        <v>46007.68324074074</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>12</v>
@@ -1542,13 +1542,13 @@
         <v>27</v>
       </c>
       <c r="B15" s="2">
-        <v>46007.32942129629</v>
+        <v>46007.33047453704</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="2">
-        <v>46007.69011574074</v>
+        <v>46007.6875</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>12</v>
@@ -1557,7 +1557,7 @@
         <v>13</v>
       </c>
       <c r="G15" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
@@ -1574,13 +1574,13 @@
         <v>28</v>
       </c>
       <c r="B16" s="2">
-        <v>46007.32229166666</v>
+        <v>46007.32409722222</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="2">
-        <v>46007.69791666666</v>
+        <v>46007.70688657407</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>12</v>
@@ -1589,7 +1589,7 @@
         <v>13</v>
       </c>
       <c r="G16" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H16" s="2">
         <v>0</v>
@@ -1606,13 +1606,13 @@
         <v>29</v>
       </c>
       <c r="B17" s="2">
-        <v>46007.32863425926</v>
+        <v>46007.35024305555</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="2">
-        <v>46007.6925462963</v>
+        <v>46007.70887731481</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>12</v>
@@ -1621,7 +1621,7 @@
         <v>13</v>
       </c>
       <c r="G17" s="2">
-        <v>19.6</v>
+        <v>18.35</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
@@ -1638,13 +1638,13 @@
         <v>30</v>
       </c>
       <c r="B18" s="2">
-        <v>46007.32585648148</v>
+        <v>46007.33373842593</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="2">
-        <v>46007.69454861111</v>
+        <v>46007.71240740741</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>12</v>
@@ -1653,7 +1653,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>31</v>
       </c>
       <c r="B19" s="2">
-        <v>46007.31453703704</v>
+        <v>46007.33122685185</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="2">
-        <v>46007.70380787037</v>
+        <v>46007.69668981482</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>12</v>
@@ -1685,7 +1685,7 @@
         <v>13</v>
       </c>
       <c r="G19" s="2">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="H19" s="2">
         <v>0</v>
@@ -1702,13 +1702,13 @@
         <v>32</v>
       </c>
       <c r="B20" s="2">
-        <v>46007.33302083334</v>
+        <v>46007.33283564815</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="2">
-        <v>46007.71336805556</v>
+        <v>46007.68991898148</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>12</v>
@@ -1734,13 +1734,13 @@
         <v>33</v>
       </c>
       <c r="B21" s="2">
-        <v>46007.33358796296</v>
+        <v>46007.32784722222</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="2">
-        <v>46007.693125</v>
+        <v>46007.68414351852</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>12</v>
@@ -1749,7 +1749,7 @@
         <v>13</v>
       </c>
       <c r="G21" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H21" s="2">
         <v>0</v>
@@ -1766,13 +1766,13 @@
         <v>34</v>
       </c>
       <c r="B22" s="2">
-        <v>46007.32873842592</v>
+        <v>46007.32734953704</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="2">
-        <v>46007.68319444444</v>
+        <v>46007.68322916667</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>12</v>
@@ -1798,13 +1798,13 @@
         <v>35</v>
       </c>
       <c r="B23" s="2">
-        <v>46007.32207175926</v>
+        <v>46007.27841435185</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="2">
-        <v>46007.71020833333</v>
+        <v>46007.73622685186</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>12</v>
@@ -1813,7 +1813,7 @@
         <v>13</v>
       </c>
       <c r="G23" s="2">
-        <v>20.7</v>
+        <v>26.8</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         <v>36</v>
       </c>
       <c r="B24" s="2">
-        <v>46007.32291666666</v>
+        <v>46007.33302083334</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="2">
-        <v>46007.69791666666</v>
+        <v>46007.71336805556</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>12</v>
@@ -1845,7 +1845,7 @@
         <v>13</v>
       </c>
       <c r="G24" s="2">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
@@ -1862,13 +1862,13 @@
         <v>37</v>
       </c>
       <c r="B25" s="2">
-        <v>46007.33122685185</v>
+        <v>46007.33094907407</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="2">
-        <v>46007.69668981482</v>
+        <v>46007.68743055555</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
@@ -1877,7 +1877,7 @@
         <v>13</v>
       </c>
       <c r="G25" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H25" s="2">
         <v>0</v>
@@ -1894,13 +1894,13 @@
         <v>38</v>
       </c>
       <c r="B26" s="2">
-        <v>46007.33208333333</v>
+        <v>46007.32733796296</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="2">
-        <v>46007.69263888889</v>
+        <v>46007.68481481481</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>12</v>
@@ -1909,7 +1909,7 @@
         <v>13</v>
       </c>
       <c r="G26" s="2">
-        <v>19.6</v>
+        <v>18.35</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -1926,13 +1926,13 @@
         <v>39</v>
       </c>
       <c r="B27" s="2">
-        <v>46007.34350694445</v>
+        <v>46007.32383101852</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D27" s="2">
-        <v>46007.68429398148</v>
+        <v>46007.68983796296</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>12</v>
@@ -1941,7 +1941,7 @@
         <v>13</v>
       </c>
       <c r="G27" s="2">
-        <v>18.7</v>
+        <v>19.6</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
@@ -1958,13 +1958,13 @@
         <v>40</v>
       </c>
       <c r="B28" s="2">
-        <v>46007.33373842593</v>
+        <v>46007.31453703704</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="2">
-        <v>46007.71240740741</v>
+        <v>46007.70380787037</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>12</v>
@@ -1990,13 +1990,13 @@
         <v>41</v>
       </c>
       <c r="B29" s="2">
-        <v>46007.32383101852</v>
+        <v>46007.32873842592</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="2">
-        <v>46007.68983796296</v>
+        <v>46007.68319444444</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -2005,7 +2005,7 @@
         <v>13</v>
       </c>
       <c r="G29" s="2">
-        <v>19.6</v>
+        <v>18.35</v>
       </c>
       <c r="H29" s="2">
         <v>0</v>
@@ -2022,13 +2022,13 @@
         <v>42</v>
       </c>
       <c r="B30" s="2">
-        <v>46007.33283564815</v>
+        <v>46007.33358796296</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D30" s="2">
-        <v>46007.68991898148</v>
+        <v>46007.693125</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>12</v>
@@ -2037,7 +2037,7 @@
         <v>13</v>
       </c>
       <c r="G30" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
@@ -2054,13 +2054,13 @@
         <v>43</v>
       </c>
       <c r="B31" s="2">
-        <v>46007.33370370371</v>
+        <v>46007.33141203703</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D31" s="2">
-        <v>46007.625</v>
+        <v>46007.70413194445</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
@@ -2069,7 +2069,7 @@
         <v>13</v>
       </c>
       <c r="G31" s="2">
-        <v>20.95</v>
+        <v>19.6</v>
       </c>
       <c r="H31" s="2">
         <v>0</v>
@@ -2118,13 +2118,13 @@
         <v>47</v>
       </c>
       <c r="B33" s="2">
-        <v>46007.28868055555</v>
+        <v>46007.29140046296</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="2">
-        <v>46007.73002314815</v>
+        <v>46007.70833333334</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>12</v>
@@ -2133,7 +2133,7 @@
         <v>45</v>
       </c>
       <c r="G33" s="2">
-        <v>20.2</v>
+        <v>22.4</v>
       </c>
       <c r="H33" s="2">
         <v>0</v>
@@ -2150,18 +2150,22 @@
         <v>48</v>
       </c>
       <c r="B34" s="2">
-        <v>46007.29140046296</v>
+        <v>46007.28868055555</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+      <c r="D34" s="2">
+        <v>46007.73002314815</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F34" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G34" s="2">
-        <v>22.4</v>
+        <v>20.2</v>
       </c>
       <c r="H34" s="2">
         <v>0</v>
@@ -2178,13 +2182,13 @@
         <v>49</v>
       </c>
       <c r="B35" s="2">
-        <v>46007.66</v>
+        <v>46007.73481481482</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D35" s="2">
-        <v>46007.8777662037</v>
+        <v>46007.85018518518</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>12</v>
@@ -2210,13 +2214,13 @@
         <v>52</v>
       </c>
       <c r="B36" s="2">
-        <v>46007.29188657407</v>
+        <v>46007.50827546296</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D36" s="2">
-        <v>46007.72993055556</v>
+        <v>46007.875</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>12</v>
@@ -2225,7 +2229,7 @@
         <v>50</v>
       </c>
       <c r="G36" s="2">
-        <v>30.75</v>
+        <v>23</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
@@ -2242,13 +2246,13 @@
         <v>53</v>
       </c>
       <c r="B37" s="2">
-        <v>46007.73481481482</v>
+        <v>46007.29188657407</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D37" s="2">
-        <v>46007.85018518518</v>
+        <v>46007.72993055556</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
@@ -2257,7 +2261,7 @@
         <v>50</v>
       </c>
       <c r="G37" s="2">
-        <v>20.2</v>
+        <v>30.75</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -2274,13 +2278,13 @@
         <v>54</v>
       </c>
       <c r="B38" s="2">
-        <v>46007.00408564815</v>
+        <v>46007.66</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D38" s="2">
-        <v>46007.49696759259</v>
+        <v>46007.8777662037</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>12</v>
@@ -2306,13 +2310,13 @@
         <v>55</v>
       </c>
       <c r="B39" s="2">
-        <v>46007.00162037037</v>
+        <v>46007.49490740741</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D39" s="2">
-        <v>46007.45174768518</v>
+        <v>46007.90277777778</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>12</v>
@@ -2338,18 +2342,22 @@
         <v>56</v>
       </c>
       <c r="B40" s="2">
-        <v>46007.50827546296</v>
+        <v>46007.00162037037</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+      <c r="D40" s="2">
+        <v>46007.45174768518</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F40" s="2" t="s">
         <v>50</v>
       </c>
       <c r="G40" s="2">
-        <v>23</v>
+        <v>20.2</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -2366,13 +2374,13 @@
         <v>57</v>
       </c>
       <c r="B41" s="2">
-        <v>46007.49490740741</v>
+        <v>46007.00408564815</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D41" s="2">
-        <v>46007.90277777778</v>
+        <v>46007.49696759259</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>12</v>
@@ -2398,13 +2406,13 @@
         <v>58</v>
       </c>
       <c r="B42" s="2">
-        <v>46007.31092592593</v>
+        <v>46007.07579861111</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D42" s="2">
-        <v>46007.72763888889</v>
+        <v>46007.3940162037</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>12</v>
@@ -2413,7 +2421,7 @@
         <v>59</v>
       </c>
       <c r="G42" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -2430,13 +2438,13 @@
         <v>61</v>
       </c>
       <c r="B43" s="2">
-        <v>46007.07579861111</v>
+        <v>46007.31240740741</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D43" s="2">
-        <v>46007.3940162037</v>
+        <v>46007.73458333333</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>12</v>
@@ -2445,7 +2453,7 @@
         <v>59</v>
       </c>
       <c r="G43" s="2">
-        <v>23</v>
+        <v>18.6</v>
       </c>
       <c r="H43" s="2">
         <v>0</v>
@@ -2459,16 +2467,16 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B44" s="2">
-        <v>46007.07583333334</v>
+        <v>46007.31092592593</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D44" s="2">
-        <v>46007.3940162037</v>
+        <v>46007.72763888889</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>12</v>
@@ -2477,7 +2485,7 @@
         <v>59</v>
       </c>
       <c r="G44" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H44" s="2">
         <v>0</v>
@@ -2491,16 +2499,16 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B45" s="2">
-        <v>46007.31240740741</v>
+        <v>46007.07583333334</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D45" s="2">
-        <v>46007.73458333333</v>
+        <v>46007.3940162037</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>12</v>
@@ -2509,7 +2517,7 @@
         <v>59</v>
       </c>
       <c r="G45" s="2">
-        <v>18.6</v>
+        <v>23</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -2646,13 +2654,13 @@
         <v>69</v>
       </c>
       <c r="B50" s="2">
-        <v>46007.53047453704</v>
+        <v>46007.28895833333</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="2">
-        <v>46007.74020833334</v>
+        <v>46007.50989583333</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>12</v>
@@ -2678,13 +2686,13 @@
         <v>69</v>
       </c>
       <c r="B51" s="2">
-        <v>46007.28895833333</v>
+        <v>46007.53047453704</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D51" s="2">
-        <v>46007.50989583333</v>
+        <v>46007.74020833334</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>12</v>
@@ -2710,13 +2718,13 @@
         <v>72</v>
       </c>
       <c r="B52" s="2">
-        <v>46007.31581018519</v>
+        <v>46007.35416666666</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D52" s="2">
-        <v>46007.71991898148</v>
+        <v>46007.73565972222</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>12</v>
@@ -2725,7 +2733,7 @@
         <v>73</v>
       </c>
       <c r="G52" s="2">
-        <v>22.4</v>
+        <v>24.8</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2742,13 +2750,13 @@
         <v>75</v>
       </c>
       <c r="B53" s="2">
-        <v>46007.31140046296</v>
+        <v>46007.31645833333</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D53" s="2">
-        <v>46007.72983796296</v>
+        <v>46007.73611111111</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>12</v>
@@ -2757,7 +2765,7 @@
         <v>73</v>
       </c>
       <c r="G53" s="2">
-        <v>20.95</v>
+        <v>24.45</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -2806,13 +2814,13 @@
         <v>77</v>
       </c>
       <c r="B55" s="2">
-        <v>46007.32284722223</v>
+        <v>46007.32126157408</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D55" s="2">
-        <v>46007.73584490741</v>
+        <v>46007.73368055555</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>12</v>
@@ -2821,7 +2829,7 @@
         <v>73</v>
       </c>
       <c r="G55" s="2">
-        <v>19.6</v>
+        <v>20.95</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -2838,13 +2846,13 @@
         <v>78</v>
       </c>
       <c r="B56" s="2">
-        <v>46007.32392361111</v>
+        <v>46007.32284722223</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D56" s="2">
-        <v>46007.49866898148</v>
+        <v>46007.73584490741</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>12</v>
@@ -2853,7 +2861,7 @@
         <v>73</v>
       </c>
       <c r="G56" s="2">
-        <v>23</v>
+        <v>19.6</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
@@ -2870,13 +2878,13 @@
         <v>79</v>
       </c>
       <c r="B57" s="2">
-        <v>46007.32126157408</v>
+        <v>46007.32392361111</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D57" s="2">
-        <v>46007.73368055555</v>
+        <v>46007.49866898148</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>12</v>
@@ -2885,7 +2893,7 @@
         <v>73</v>
       </c>
       <c r="G57" s="2">
-        <v>20.95</v>
+        <v>23</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -2902,13 +2910,13 @@
         <v>80</v>
       </c>
       <c r="B58" s="2">
-        <v>46007.31805555556</v>
+        <v>46007.33047453704</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D58" s="2">
-        <v>46007.73365740741</v>
+        <v>46007.73633101852</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>12</v>
@@ -2917,7 +2925,7 @@
         <v>73</v>
       </c>
       <c r="G58" s="2">
-        <v>20.95</v>
+        <v>19.25</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -2934,13 +2942,13 @@
         <v>81</v>
       </c>
       <c r="B59" s="2">
-        <v>46007.33047453704</v>
+        <v>46007.31140046296</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D59" s="2">
-        <v>46007.73633101852</v>
+        <v>46007.72983796296</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>12</v>
@@ -2949,7 +2957,7 @@
         <v>73</v>
       </c>
       <c r="G59" s="2">
-        <v>19.25</v>
+        <v>20.95</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -2966,13 +2974,13 @@
         <v>82</v>
       </c>
       <c r="B60" s="2">
-        <v>46007.31645833333</v>
+        <v>46007.32082175926</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D60" s="2">
-        <v>46007.73611111111</v>
+        <v>46007.73688657407</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>12</v>
@@ -2981,7 +2989,7 @@
         <v>73</v>
       </c>
       <c r="G60" s="2">
-        <v>24.45</v>
+        <v>19.25</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>
@@ -2998,25 +3006,25 @@
         <v>83</v>
       </c>
       <c r="B61" s="2">
-        <v>46007.35416666666</v>
+        <v>46007.33333333334</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="D61" s="2">
-        <v>46007.73565972222</v>
+        <v>46007.33333333334</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>73</v>
       </c>
       <c r="G61" s="2">
-        <v>24.8</v>
+        <v>20.7</v>
       </c>
       <c r="H61" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I61" s="2">
         <v>0</v>
@@ -3027,16 +3035,16 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B62" s="2">
-        <v>46007.32472222222</v>
+        <v>46007.31581018519</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D62" s="2">
-        <v>46007.73939814815</v>
+        <v>46007.71991898148</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>12</v>
@@ -3045,7 +3053,7 @@
         <v>73</v>
       </c>
       <c r="G62" s="2">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
@@ -3059,16 +3067,16 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B63" s="2">
-        <v>46007.32082175926</v>
+        <v>46007.31805555556</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="2">
-        <v>46007.73688657407</v>
+        <v>46007.73365740741</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>12</v>
@@ -3077,7 +3085,7 @@
         <v>73</v>
       </c>
       <c r="G63" s="2">
-        <v>19.25</v>
+        <v>20.95</v>
       </c>
       <c r="H63" s="2">
         <v>0</v>
@@ -3091,28 +3099,28 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B64" s="2">
-        <v>46007.33333333334</v>
+        <v>46007.32472222222</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="D64" s="2">
-        <v>46007.33333333334</v>
+        <v>46007.73939814815</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>73</v>
       </c>
       <c r="G64" s="2">
-        <v>20.7</v>
+        <v>23</v>
       </c>
       <c r="H64" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I64" s="2">
         <v>0</v>
@@ -3126,13 +3134,13 @@
         <v>88</v>
       </c>
       <c r="B65" s="2">
-        <v>46007.32146990741</v>
+        <v>46007.32520833334</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D65" s="2">
-        <v>46007.47895833333</v>
+        <v>46007.72858796296</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>12</v>
@@ -3141,7 +3149,7 @@
         <v>89</v>
       </c>
       <c r="G65" s="2">
-        <v>19.25</v>
+        <v>22.4</v>
       </c>
       <c r="H65" s="2">
         <v>0</v>
@@ -3158,13 +3166,13 @@
         <v>91</v>
       </c>
       <c r="B66" s="2">
-        <v>46007.32520833334</v>
+        <v>46007.33174768519</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D66" s="2">
-        <v>46007.72858796296</v>
+        <v>46007.74184027778</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>12</v>
@@ -3173,7 +3181,7 @@
         <v>89</v>
       </c>
       <c r="G66" s="2">
-        <v>22.4</v>
+        <v>22.75</v>
       </c>
       <c r="H66" s="2">
         <v>0</v>
@@ -3190,13 +3198,13 @@
         <v>92</v>
       </c>
       <c r="B67" s="2">
-        <v>46007.32313657407</v>
+        <v>46007.31825231481</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D67" s="2">
-        <v>46007.50314814815</v>
+        <v>46007.61453703704</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>12</v>
@@ -3222,18 +3230,22 @@
         <v>93</v>
       </c>
       <c r="B68" s="2">
-        <v>46007.32508101852</v>
+        <v>46007.32320601852</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
+      <c r="D68" s="2">
+        <v>46007.60640046297</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F68" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G68" s="2">
-        <v>19.6</v>
+        <v>19.25</v>
       </c>
       <c r="H68" s="2">
         <v>0</v>
@@ -3250,22 +3262,18 @@
         <v>94</v>
       </c>
       <c r="B69" s="2">
-        <v>46007.31825231481</v>
+        <v>46007.32508101852</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D69" s="2">
-        <v>46007.61453703704</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G69" s="2">
-        <v>19.75</v>
+        <v>19.6</v>
       </c>
       <c r="H69" s="2">
         <v>0</v>
@@ -3282,13 +3290,13 @@
         <v>95</v>
       </c>
       <c r="B70" s="2">
-        <v>46007.32466435185</v>
+        <v>46007.32146990741</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D70" s="2">
-        <v>46007.49305555555</v>
+        <v>46007.47895833333</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>12</v>
@@ -3297,7 +3305,7 @@
         <v>89</v>
       </c>
       <c r="G70" s="2">
-        <v>19.35</v>
+        <v>19.25</v>
       </c>
       <c r="H70" s="2">
         <v>0</v>
@@ -3314,13 +3322,13 @@
         <v>96</v>
       </c>
       <c r="B71" s="2">
-        <v>46007.33174768519</v>
+        <v>46007.32466435185</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D71" s="2">
-        <v>46007.74184027778</v>
+        <v>46007.49305555555</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>12</v>
@@ -3329,7 +3337,7 @@
         <v>89</v>
       </c>
       <c r="G71" s="2">
-        <v>22.75</v>
+        <v>19.35</v>
       </c>
       <c r="H71" s="2">
         <v>0</v>
@@ -3346,13 +3354,13 @@
         <v>97</v>
       </c>
       <c r="B72" s="2">
-        <v>46007.32320601852</v>
+        <v>46007.32313657407</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D72" s="2">
-        <v>46007.60640046297</v>
+        <v>46007.50314814815</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>12</v>
@@ -3361,7 +3369,7 @@
         <v>89</v>
       </c>
       <c r="G72" s="2">
-        <v>19.25</v>
+        <v>19.75</v>
       </c>
       <c r="H72" s="2">
         <v>0</v>
@@ -3378,13 +3386,13 @@
         <v>98</v>
       </c>
       <c r="B73" s="2">
-        <v>46007.32251157407</v>
+        <v>46007.32268518519</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D73" s="2">
-        <v>46007.68957175926</v>
+        <v>46007.68872685185</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>12</v>
@@ -3393,7 +3401,7 @@
         <v>99</v>
       </c>
       <c r="G73" s="2">
-        <v>23.35</v>
+        <v>23</v>
       </c>
       <c r="H73" s="2">
         <v>0</v>
@@ -3442,13 +3450,13 @@
         <v>102</v>
       </c>
       <c r="B75" s="2">
-        <v>46007.32268518519</v>
+        <v>46007.32251157407</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D75" s="2">
-        <v>46007.68872685185</v>
+        <v>46007.68957175926</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>12</v>
@@ -3457,7 +3465,7 @@
         <v>99</v>
       </c>
       <c r="G75" s="2">
-        <v>23</v>
+        <v>23.35</v>
       </c>
       <c r="H75" s="2">
         <v>0</v>
@@ -3474,13 +3482,13 @@
         <v>103</v>
       </c>
       <c r="B76" s="2">
-        <v>46007.53320601852</v>
+        <v>46007.54084490741</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D76" s="2">
-        <v>46007.72414351852</v>
+        <v>46007.72559027778</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>12</v>
@@ -3503,25 +3511,21 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B77" s="2">
-        <v>46007.32021990741</v>
+        <v>46007.58866898148</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="2">
-        <v>46007.51498842592</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
         <v>104</v>
       </c>
       <c r="G77" s="2">
-        <v>18.35</v>
+        <v>19.6</v>
       </c>
       <c r="H77" s="2">
         <v>0</v>
@@ -3535,16 +3539,16 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B78" s="2">
-        <v>46007.67640046297</v>
+        <v>46007.33680555555</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D78" s="2">
-        <v>46007.69515046296</v>
+        <v>46007.72434027777</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>12</v>
@@ -3553,7 +3557,7 @@
         <v>104</v>
       </c>
       <c r="G78" s="2">
-        <v>19.25</v>
+        <v>18.7</v>
       </c>
       <c r="H78" s="2">
         <v>0</v>
@@ -3567,16 +3571,16 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B79" s="2">
-        <v>46007.32300925926</v>
+        <v>46007.34150462963</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D79" s="2">
-        <v>46007.54361111111</v>
+        <v>46007.56024305556</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>12</v>
@@ -3585,7 +3589,7 @@
         <v>104</v>
       </c>
       <c r="G79" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3602,18 +3606,22 @@
         <v>108</v>
       </c>
       <c r="B80" s="2">
-        <v>46007.58866898148</v>
+        <v>46007.57622685185</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
+      <c r="D80" s="2">
+        <v>46007.72405092593</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F80" s="2" t="s">
         <v>104</v>
       </c>
       <c r="G80" s="2">
-        <v>19.6</v>
+        <v>18.35</v>
       </c>
       <c r="H80" s="2">
         <v>0</v>
@@ -3627,16 +3635,16 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B81" s="2">
-        <v>46007.31895833334</v>
+        <v>46007.32300925926</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D81" s="2">
-        <v>46007.56732638889</v>
+        <v>46007.54361111111</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>12</v>
@@ -3645,7 +3653,7 @@
         <v>104</v>
       </c>
       <c r="G81" s="2">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="H81" s="2">
         <v>0</v>
@@ -3662,13 +3670,13 @@
         <v>109</v>
       </c>
       <c r="B82" s="2">
-        <v>46007.31946759259</v>
+        <v>46007.5499537037</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D82" s="2">
-        <v>46007.52570601852</v>
+        <v>46007.72465277778</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>12</v>
@@ -3677,7 +3685,7 @@
         <v>104</v>
       </c>
       <c r="G82" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H82" s="2">
         <v>0</v>
@@ -3694,13 +3702,13 @@
         <v>110</v>
       </c>
       <c r="B83" s="2">
-        <v>46007.60548611111</v>
+        <v>46007.32346064815</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D83" s="2">
-        <v>46007.72375</v>
+        <v>46007.54369212963</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>12</v>
@@ -3709,7 +3717,7 @@
         <v>104</v>
       </c>
       <c r="G83" s="2">
-        <v>23</v>
+        <v>18.6</v>
       </c>
       <c r="H83" s="2">
         <v>0</v>
@@ -3723,16 +3731,16 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B84" s="2">
-        <v>46007.30252314815</v>
+        <v>46007.31895833334</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D84" s="2">
-        <v>46007.59231481481</v>
+        <v>46007.56732638889</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>12</v>
@@ -3741,7 +3749,7 @@
         <v>104</v>
       </c>
       <c r="G84" s="2">
-        <v>23</v>
+        <v>19.6</v>
       </c>
       <c r="H84" s="2">
         <v>0</v>
@@ -3755,16 +3763,16 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B85" s="2">
-        <v>46007.61052083333</v>
+        <v>46007.58949074074</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D85" s="2">
-        <v>46007.72451388889</v>
+        <v>46007.72456018518</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>12</v>
@@ -3790,13 +3798,13 @@
         <v>111</v>
       </c>
       <c r="B86" s="2">
-        <v>46007.3284375</v>
+        <v>46007.63060185185</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D86" s="2">
-        <v>46007.59623842593</v>
+        <v>46007.7237962963</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>12</v>
@@ -3805,7 +3813,7 @@
         <v>104</v>
       </c>
       <c r="G86" s="2">
-        <v>18.6</v>
+        <v>19.75</v>
       </c>
       <c r="H86" s="2">
         <v>0</v>
@@ -3822,13 +3830,13 @@
         <v>112</v>
       </c>
       <c r="B87" s="2">
-        <v>46007.3235300926</v>
+        <v>46007.3284375</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D87" s="2">
-        <v>46007.72987268519</v>
+        <v>46007.59623842593</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>12</v>
@@ -3851,16 +3859,16 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B88" s="2">
-        <v>46007.5499537037</v>
+        <v>46007.61052083333</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D88" s="2">
-        <v>46007.72465277778</v>
+        <v>46007.72451388889</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>12</v>
@@ -3869,7 +3877,7 @@
         <v>104</v>
       </c>
       <c r="G88" s="2">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="H88" s="2">
         <v>0</v>
@@ -3883,16 +3891,16 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B89" s="2">
-        <v>46007.54084490741</v>
+        <v>46007.30252314815</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D89" s="2">
-        <v>46007.72559027778</v>
+        <v>46007.59231481481</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>12</v>
@@ -3901,7 +3909,7 @@
         <v>104</v>
       </c>
       <c r="G89" s="2">
-        <v>18.35</v>
+        <v>23</v>
       </c>
       <c r="H89" s="2">
         <v>0</v>
@@ -3918,13 +3926,13 @@
         <v>113</v>
       </c>
       <c r="B90" s="2">
-        <v>46007.58949074074</v>
+        <v>46007.60548611111</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D90" s="2">
-        <v>46007.72456018518</v>
+        <v>46007.72375</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>12</v>
@@ -3933,7 +3941,7 @@
         <v>104</v>
       </c>
       <c r="G90" s="2">
-        <v>18.6</v>
+        <v>23</v>
       </c>
       <c r="H90" s="2">
         <v>0</v>
@@ -3947,16 +3955,16 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B91" s="2">
-        <v>46007.33680555555</v>
+        <v>46007.31946759259</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D91" s="2">
-        <v>46007.72434027777</v>
+        <v>46007.52570601852</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>12</v>
@@ -3965,7 +3973,7 @@
         <v>104</v>
       </c>
       <c r="G91" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H91" s="2">
         <v>0</v>
@@ -3979,16 +3987,16 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B92" s="2">
-        <v>46007.34150462963</v>
+        <v>46007.53320601852</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D92" s="2">
-        <v>46007.56024305556</v>
+        <v>46007.72414351852</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>12</v>
@@ -4011,16 +4019,16 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B93" s="2">
-        <v>46007.32346064815</v>
+        <v>46007.32369212963</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D93" s="2">
-        <v>46007.54369212963</v>
+        <v>46007.61914351852</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>12</v>
@@ -4029,7 +4037,7 @@
         <v>104</v>
       </c>
       <c r="G93" s="2">
-        <v>18.6</v>
+        <v>19.75</v>
       </c>
       <c r="H93" s="2">
         <v>0</v>
@@ -4043,16 +4051,16 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B94" s="2">
-        <v>46007.32369212963</v>
+        <v>46007.3235300926</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D94" s="2">
-        <v>46007.61914351852</v>
+        <v>46007.72987268519</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>12</v>
@@ -4061,7 +4069,7 @@
         <v>104</v>
       </c>
       <c r="G94" s="2">
-        <v>19.75</v>
+        <v>18.6</v>
       </c>
       <c r="H94" s="2">
         <v>0</v>
@@ -4075,16 +4083,16 @@
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B95" s="2">
-        <v>46007.57622685185</v>
+        <v>46007.67640046297</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D95" s="2">
-        <v>46007.72405092593</v>
+        <v>46007.69515046296</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>12</v>
@@ -4093,7 +4101,7 @@
         <v>104</v>
       </c>
       <c r="G95" s="2">
-        <v>18.35</v>
+        <v>19.25</v>
       </c>
       <c r="H95" s="2">
         <v>0</v>
@@ -4107,16 +4115,16 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B96" s="2">
-        <v>46007.63060185185</v>
+        <v>46007.32021990741</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D96" s="2">
-        <v>46007.7237962963</v>
+        <v>46007.51498842592</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>12</v>
@@ -4125,7 +4133,7 @@
         <v>104</v>
       </c>
       <c r="G96" s="2">
-        <v>19.75</v>
+        <v>18.35</v>
       </c>
       <c r="H96" s="2">
         <v>0</v>
@@ -4270,13 +4278,13 @@
         <v>124</v>
       </c>
       <c r="B101" s="2">
-        <v>46007.54909722223</v>
+        <v>46007.37464120371</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D101" s="2">
-        <v>46007.69951388889</v>
+        <v>46007.72012731482</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>12</v>
@@ -4285,7 +4293,7 @@
         <v>125</v>
       </c>
       <c r="G101" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H101" s="2">
         <v>0</v>
@@ -4299,7 +4307,7 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B102" s="2">
         <v>46007.33373842593</v>
@@ -4331,7 +4339,7 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B103" s="2">
         <v>46007.31704861111</v>
@@ -4363,16 +4371,16 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B104" s="2">
-        <v>46007.37464120371</v>
+        <v>46007.54909722223</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D104" s="2">
-        <v>46007.72012731482</v>
+        <v>46007.69951388889</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>12</v>
@@ -4381,7 +4389,7 @@
         <v>125</v>
       </c>
       <c r="G104" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H104" s="2">
         <v>0</v>
@@ -4433,13 +4441,13 @@
         <v>46007.33333333334</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D106" s="2">
         <v>46007.33333333334</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>133</v>
@@ -4462,13 +4470,13 @@
         <v>135</v>
       </c>
       <c r="B107" s="2">
-        <v>46007.35180555555</v>
+        <v>46007.36309027778</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D107" s="2">
-        <v>46007.68700231481</v>
+        <v>46007.56648148148</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>12</v>
@@ -4477,7 +4485,7 @@
         <v>133</v>
       </c>
       <c r="G107" s="2">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="H107" s="2">
         <v>0</v>
@@ -4494,13 +4502,13 @@
         <v>136</v>
       </c>
       <c r="B108" s="2">
-        <v>46007.31447916666</v>
+        <v>46007.35180555555</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D108" s="2">
-        <v>46007.62649305556</v>
+        <v>46007.68700231481</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>12</v>
@@ -4509,7 +4517,7 @@
         <v>133</v>
       </c>
       <c r="G108" s="2">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="H108" s="2">
         <v>0</v>
@@ -4526,13 +4534,13 @@
         <v>137</v>
       </c>
       <c r="B109" s="2">
-        <v>46007.36309027778</v>
+        <v>46007.33133101852</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D109" s="2">
-        <v>46007.56648148148</v>
+        <v>46007.72393518518</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>12</v>
@@ -4541,7 +4549,7 @@
         <v>133</v>
       </c>
       <c r="G109" s="2">
-        <v>18.7</v>
+        <v>22.4</v>
       </c>
       <c r="H109" s="2">
         <v>0</v>
@@ -4558,13 +4566,13 @@
         <v>138</v>
       </c>
       <c r="B110" s="2">
-        <v>46007.4652199074</v>
+        <v>46007.385</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D110" s="2">
-        <v>46007.46523148148</v>
+        <v>46007.6991087963</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>12</v>
@@ -4573,7 +4581,7 @@
         <v>133</v>
       </c>
       <c r="G110" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H110" s="2">
         <v>0</v>
@@ -4590,13 +4598,13 @@
         <v>139</v>
       </c>
       <c r="B111" s="2">
-        <v>46007.33133101852</v>
+        <v>46007.36332175926</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D111" s="2">
-        <v>46007.72393518518</v>
+        <v>46007.6875</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>12</v>
@@ -4605,7 +4613,7 @@
         <v>133</v>
       </c>
       <c r="G111" s="2">
-        <v>22.4</v>
+        <v>18.35</v>
       </c>
       <c r="H111" s="2">
         <v>0</v>
@@ -4622,13 +4630,13 @@
         <v>140</v>
       </c>
       <c r="B112" s="2">
-        <v>46007.385</v>
+        <v>46007.24976851852</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D112" s="2">
-        <v>46007.6991087963</v>
+        <v>46007.56631944444</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>12</v>
@@ -4637,7 +4645,7 @@
         <v>133</v>
       </c>
       <c r="G112" s="2">
-        <v>18.35</v>
+        <v>22.4</v>
       </c>
       <c r="H112" s="2">
         <v>0</v>
@@ -4654,13 +4662,13 @@
         <v>141</v>
       </c>
       <c r="B113" s="2">
-        <v>46007.36332175926</v>
+        <v>46007.36833333333</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D113" s="2">
-        <v>46007.6875</v>
+        <v>46007.7392824074</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>12</v>
@@ -4686,13 +4694,13 @@
         <v>142</v>
       </c>
       <c r="B114" s="2">
-        <v>46007.24976851852</v>
+        <v>46007.31447916666</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D114" s="2">
-        <v>46007.56631944444</v>
+        <v>46007.62649305556</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>12</v>
@@ -4701,7 +4709,7 @@
         <v>133</v>
       </c>
       <c r="G114" s="2">
-        <v>22.4</v>
+        <v>18.7</v>
       </c>
       <c r="H114" s="2">
         <v>0</v>
@@ -4750,13 +4758,13 @@
         <v>144</v>
       </c>
       <c r="B116" s="2">
-        <v>46007.36833333333</v>
+        <v>46007.4652199074</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D116" s="2">
-        <v>46007.7392824074</v>
+        <v>46007.46523148148</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>12</v>
@@ -4765,7 +4773,7 @@
         <v>133</v>
       </c>
       <c r="G116" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H116" s="2">
         <v>0</v>
@@ -4782,13 +4790,13 @@
         <v>145</v>
       </c>
       <c r="B117" s="2">
-        <v>46007.30570601852</v>
+        <v>46007.3717824074</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D117" s="2">
-        <v>46007.58572916667</v>
+        <v>46007.68483796297</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>12</v>
@@ -4811,16 +4819,16 @@
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B118" s="2">
-        <v>46007.46533564815</v>
+        <v>46007.33049768519</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="2">
-        <v>46007.69047453703</v>
+        <v>46007.62881944444</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>12</v>
@@ -4829,7 +4837,7 @@
         <v>146</v>
       </c>
       <c r="G118" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H118" s="2">
         <v>0</v>
@@ -4843,16 +4851,16 @@
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B119" s="2">
-        <v>46007.27618055556</v>
+        <v>46007.31015046296</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D119" s="2">
-        <v>46007.65038194445</v>
+        <v>46007.58297453704</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>12</v>
@@ -4861,7 +4869,7 @@
         <v>146</v>
       </c>
       <c r="G119" s="2">
-        <v>19.65</v>
+        <v>18.35</v>
       </c>
       <c r="H119" s="2">
         <v>0</v>
@@ -4875,16 +4883,16 @@
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B120" s="2">
-        <v>46007.3074537037</v>
+        <v>46007.50731481481</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D120" s="2">
-        <v>46007.59822916667</v>
+        <v>46007.51900462963</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>12</v>
@@ -4893,7 +4901,7 @@
         <v>146</v>
       </c>
       <c r="G120" s="2">
-        <v>18.35</v>
+        <v>23.35</v>
       </c>
       <c r="H120" s="2">
         <v>0</v>
@@ -4910,25 +4918,25 @@
         <v>150</v>
       </c>
       <c r="B121" s="2">
-        <v>46007.33333333334</v>
+        <v>46007.86049768519</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="D121" s="2">
-        <v>46007.33333333334</v>
+        <v>46007.90716435185</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>146</v>
       </c>
       <c r="G121" s="2">
-        <v>18.6</v>
+        <v>23.35</v>
       </c>
       <c r="H121" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I121" s="2">
         <v>0</v>
@@ -4942,13 +4950,13 @@
         <v>151</v>
       </c>
       <c r="B122" s="2">
-        <v>46007.45578703703</v>
+        <v>46007.33239583333</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D122" s="2">
-        <v>46007.68614583334</v>
+        <v>46007.73763888889</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>12</v>
@@ -4974,13 +4982,13 @@
         <v>152</v>
       </c>
       <c r="B123" s="2">
-        <v>46007.46849537037</v>
+        <v>46007.26427083334</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D123" s="2">
-        <v>46007.68549768518</v>
+        <v>46007.48240740741</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>12</v>
@@ -4989,7 +4997,7 @@
         <v>146</v>
       </c>
       <c r="G123" s="2">
-        <v>18.6</v>
+        <v>18.35</v>
       </c>
       <c r="H123" s="2">
         <v>0</v>
@@ -5006,16 +5014,16 @@
         <v>153</v>
       </c>
       <c r="B124" s="2">
-        <v>46007.33333333334</v>
+        <v>46007.27743055556</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="D124" s="2">
-        <v>46007.33333333334</v>
+        <v>46007.64645833334</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>146</v>
@@ -5024,7 +5032,7 @@
         <v>18.35</v>
       </c>
       <c r="H124" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I124" s="2">
         <v>0</v>
@@ -5038,25 +5046,25 @@
         <v>154</v>
       </c>
       <c r="B125" s="2">
-        <v>46007.30578703704</v>
+        <v>46007.33333333334</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="D125" s="2">
-        <v>46007.61978009259</v>
+        <v>46007.33333333334</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>146</v>
       </c>
       <c r="G125" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H125" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I125" s="2">
         <v>0</v>
@@ -5070,13 +5078,13 @@
         <v>155</v>
       </c>
       <c r="B126" s="2">
-        <v>46007.3717824074</v>
+        <v>46007.46849537037</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D126" s="2">
-        <v>46007.68483796297</v>
+        <v>46007.68549768518</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>12</v>
@@ -5085,7 +5093,7 @@
         <v>146</v>
       </c>
       <c r="G126" s="2">
-        <v>18.35</v>
+        <v>18.6</v>
       </c>
       <c r="H126" s="2">
         <v>0</v>
@@ -5102,25 +5110,25 @@
         <v>156</v>
       </c>
       <c r="B127" s="2">
-        <v>46007.31396990741</v>
+        <v>46007.33333333334</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="D127" s="2">
-        <v>46007.58420138889</v>
+        <v>46007.33333333334</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>146</v>
       </c>
       <c r="G127" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H127" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I127" s="2">
         <v>0</v>
@@ -5134,13 +5142,13 @@
         <v>157</v>
       </c>
       <c r="B128" s="2">
-        <v>46007.31015046296</v>
+        <v>46007.30578703704</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D128" s="2">
-        <v>46007.58297453704</v>
+        <v>46007.61978009259</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>12</v>
@@ -5166,13 +5174,13 @@
         <v>158</v>
       </c>
       <c r="B129" s="2">
-        <v>46007.86049768519</v>
+        <v>46007.29804398148</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D129" s="2">
-        <v>46007.90716435185</v>
+        <v>46007.73356481481</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>12</v>
@@ -5181,7 +5189,7 @@
         <v>146</v>
       </c>
       <c r="G129" s="2">
-        <v>23.35</v>
+        <v>21.8</v>
       </c>
       <c r="H129" s="2">
         <v>0</v>
@@ -5195,16 +5203,16 @@
     </row>
     <row r="130" spans="1:10">
       <c r="A130" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B130" s="2">
-        <v>46007.50731481481</v>
+        <v>46007.3074537037</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D130" s="2">
-        <v>46007.51900462963</v>
+        <v>46007.59822916667</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>12</v>
@@ -5213,7 +5221,7 @@
         <v>146</v>
       </c>
       <c r="G130" s="2">
-        <v>23.35</v>
+        <v>18.35</v>
       </c>
       <c r="H130" s="2">
         <v>0</v>
@@ -5227,16 +5235,16 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B131" s="2">
-        <v>46007.33049768519</v>
+        <v>46007.4575</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D131" s="2">
-        <v>46007.62881944444</v>
+        <v>46007.69258101852</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>12</v>
@@ -5245,7 +5253,7 @@
         <v>146</v>
       </c>
       <c r="G131" s="2">
-        <v>18.35</v>
+        <v>20.2</v>
       </c>
       <c r="H131" s="2">
         <v>0</v>
@@ -5259,16 +5267,16 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B132" s="2">
-        <v>46007.4575</v>
+        <v>46007.31396990741</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D132" s="2">
-        <v>46007.69258101852</v>
+        <v>46007.58420138889</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>12</v>
@@ -5277,7 +5285,7 @@
         <v>146</v>
       </c>
       <c r="G132" s="2">
-        <v>20.2</v>
+        <v>18.7</v>
       </c>
       <c r="H132" s="2">
         <v>0</v>
@@ -5291,16 +5299,16 @@
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B133" s="2">
-        <v>46007.29804398148</v>
+        <v>46007.27618055556</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D133" s="2">
-        <v>46007.73356481481</v>
+        <v>46007.65038194445</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>12</v>
@@ -5309,7 +5317,7 @@
         <v>146</v>
       </c>
       <c r="G133" s="2">
-        <v>21.8</v>
+        <v>19.65</v>
       </c>
       <c r="H133" s="2">
         <v>0</v>
@@ -5323,16 +5331,16 @@
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B134" s="2">
-        <v>46007.27743055556</v>
+        <v>46007.41804398148</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D134" s="2">
-        <v>46007.64645833334</v>
+        <v>46007.69143518519</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>12</v>
@@ -5355,16 +5363,16 @@
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B135" s="2">
-        <v>46007.26427083334</v>
+        <v>46007.33081018519</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D135" s="2">
-        <v>46007.48240740741</v>
+        <v>46007.64128472222</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>12</v>
@@ -5387,16 +5395,16 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B136" s="2">
-        <v>46007.45126157408</v>
+        <v>46007.45662037037</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D136" s="2">
-        <v>46007.69297453704</v>
+        <v>46007.69665509259</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>12</v>
@@ -5405,7 +5413,7 @@
         <v>146</v>
       </c>
       <c r="G136" s="2">
-        <v>18.35</v>
+        <v>20.2</v>
       </c>
       <c r="H136" s="2">
         <v>0</v>
@@ -5419,16 +5427,16 @@
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B137" s="2">
-        <v>46007.45662037037</v>
+        <v>46007.45126157408</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D137" s="2">
-        <v>46007.69665509259</v>
+        <v>46007.69297453704</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>12</v>
@@ -5437,7 +5445,7 @@
         <v>146</v>
       </c>
       <c r="G137" s="2">
-        <v>20.2</v>
+        <v>18.35</v>
       </c>
       <c r="H137" s="2">
         <v>0</v>
@@ -5451,16 +5459,16 @@
     </row>
     <row r="138" spans="1:10">
       <c r="A138" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B138" s="2">
-        <v>46007.33081018519</v>
+        <v>46007.45578703703</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D138" s="2">
-        <v>46007.64128472222</v>
+        <v>46007.68614583334</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>12</v>
@@ -5483,16 +5491,16 @@
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="2" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="B139" s="2">
-        <v>46007.41804398148</v>
+        <v>46007.46533564815</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D139" s="2">
-        <v>46007.69143518519</v>
+        <v>46007.69047453703</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>12</v>
@@ -5501,7 +5509,7 @@
         <v>146</v>
       </c>
       <c r="G139" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H139" s="2">
         <v>0</v>
@@ -5518,13 +5526,13 @@
         <v>168</v>
       </c>
       <c r="B140" s="2">
-        <v>46007.33239583333</v>
+        <v>46007.30570601852</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D140" s="2">
-        <v>46007.73763888889</v>
+        <v>46007.58572916667</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>12</v>
@@ -5614,13 +5622,13 @@
         <v>173</v>
       </c>
       <c r="B143" s="2">
-        <v>46007.37125</v>
+        <v>46007.37421296296</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D143" s="2">
-        <v>46007.6829050926</v>
+        <v>46007.70712962963</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>12</v>
@@ -5629,7 +5637,7 @@
         <v>174</v>
       </c>
       <c r="G143" s="2">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="H143" s="2">
         <v>0</v>
@@ -5678,13 +5686,13 @@
         <v>177</v>
       </c>
       <c r="B145" s="2">
-        <v>46007.37421296296</v>
+        <v>46007.41177083334</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D145" s="2">
-        <v>46007.70712962963</v>
+        <v>46007.64855324074</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>12</v>
@@ -5710,13 +5718,13 @@
         <v>178</v>
       </c>
       <c r="B146" s="2">
-        <v>46007.41177083334</v>
+        <v>46007.37125</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D146" s="2">
-        <v>46007.64855324074</v>
+        <v>46007.6829050926</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>12</v>
@@ -5725,7 +5733,7 @@
         <v>174</v>
       </c>
       <c r="G146" s="2">
-        <v>18.35</v>
+        <v>18.7</v>
       </c>
       <c r="H146" s="2">
         <v>0</v>
@@ -5742,13 +5750,13 @@
         <v>179</v>
       </c>
       <c r="B147" s="2">
-        <v>46007.62140046297</v>
+        <v>46007.27199074074</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D147" s="2">
-        <v>46007.92081018518</v>
+        <v>46007.50893518519</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>12</v>
@@ -5757,7 +5765,7 @@
         <v>180</v>
       </c>
       <c r="G147" s="2">
-        <v>18.35</v>
+        <v>17.85</v>
       </c>
       <c r="H147" s="2">
         <v>0</v>
@@ -5774,13 +5782,13 @@
         <v>182</v>
       </c>
       <c r="B148" s="2">
-        <v>46007.27199074074</v>
+        <v>46007.62140046297</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D148" s="2">
-        <v>46007.50893518519</v>
+        <v>46007.92081018518</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>12</v>
@@ -5789,7 +5797,7 @@
         <v>180</v>
       </c>
       <c r="G148" s="2">
-        <v>17.85</v>
+        <v>18.35</v>
       </c>
       <c r="H148" s="2">
         <v>0</v>
@@ -5834,13 +5842,13 @@
         <v>184</v>
       </c>
       <c r="B150" s="2">
-        <v>46007.38203703704</v>
+        <v>46007.46082175926</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D150" s="2">
-        <v>46007.67197916667</v>
+        <v>46007.62287037037</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>12</v>
@@ -5849,7 +5857,7 @@
         <v>185</v>
       </c>
       <c r="G150" s="2">
-        <v>23</v>
+        <v>20.2</v>
       </c>
       <c r="H150" s="2">
         <v>0</v>
@@ -5930,13 +5938,13 @@
         <v>188</v>
       </c>
       <c r="B153" s="2">
-        <v>46007.37091435185</v>
+        <v>46007.38203703704</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D153" s="2">
-        <v>46007.63747685185</v>
+        <v>46007.67197916667</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>12</v>
@@ -5945,7 +5953,7 @@
         <v>185</v>
       </c>
       <c r="G153" s="2">
-        <v>20.2</v>
+        <v>23</v>
       </c>
       <c r="H153" s="2">
         <v>0</v>
@@ -5962,13 +5970,13 @@
         <v>189</v>
       </c>
       <c r="B154" s="2">
-        <v>46007.36915509259</v>
+        <v>46007.37091435185</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D154" s="2">
-        <v>46007.62287037037</v>
+        <v>46007.63747685185</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>12</v>
@@ -5991,10 +5999,10 @@
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B155" s="2">
-        <v>46007.46082175926</v>
+        <v>46007.36915509259</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>11</v>
@@ -6058,13 +6066,13 @@
         <v>193</v>
       </c>
       <c r="B157" s="2">
-        <v>46007.33333333334</v>
+        <v>46007.33739583333</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D157" s="2">
-        <v>46007.51722222222</v>
+        <v>46007.57178240741</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>12</v>
@@ -6073,7 +6081,7 @@
         <v>191</v>
       </c>
       <c r="G157" s="2">
-        <v>19.25</v>
+        <v>19.75</v>
       </c>
       <c r="H157" s="2">
         <v>0</v>
@@ -6154,13 +6162,13 @@
         <v>196</v>
       </c>
       <c r="B160" s="2">
-        <v>46007.33739583333</v>
+        <v>46007.33333333334</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D160" s="2">
-        <v>46007.57178240741</v>
+        <v>46007.51722222222</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>12</v>
@@ -6169,7 +6177,7 @@
         <v>191</v>
       </c>
       <c r="G160" s="2">
-        <v>19.75</v>
+        <v>19.25</v>
       </c>
       <c r="H160" s="2">
         <v>0</v>
@@ -6218,13 +6226,13 @@
         <v>200</v>
       </c>
       <c r="B162" s="2">
-        <v>46007.33766203704</v>
+        <v>46007.69599537037</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D162" s="2">
-        <v>46007.64625</v>
+        <v>46007.94621527778</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>12</v>
@@ -6233,7 +6241,7 @@
         <v>201</v>
       </c>
       <c r="G162" s="2">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="H162" s="2">
         <v>0</v>
@@ -6250,13 +6258,13 @@
         <v>203</v>
       </c>
       <c r="B163" s="2">
-        <v>46007.68846064815</v>
+        <v>46007.33766203704</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D163" s="2">
-        <v>46007.94665509259</v>
+        <v>46007.64625</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>12</v>
@@ -6265,7 +6273,7 @@
         <v>201</v>
       </c>
       <c r="G163" s="2">
-        <v>19.65</v>
+        <v>20.7</v>
       </c>
       <c r="H163" s="2">
         <v>0</v>
@@ -6282,13 +6290,13 @@
         <v>204</v>
       </c>
       <c r="B164" s="2">
-        <v>46007.69599537037</v>
+        <v>46007.35709490741</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D164" s="2">
-        <v>46007.94621527778</v>
+        <v>46007.57960648148</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>12</v>
@@ -6297,7 +6305,7 @@
         <v>201</v>
       </c>
       <c r="G164" s="2">
-        <v>21.2</v>
+        <v>24.8</v>
       </c>
       <c r="H164" s="2">
         <v>0</v>
@@ -6311,7 +6319,7 @@
     </row>
     <row r="165" spans="1:10">
       <c r="A165" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B165" s="2">
         <v>46007.5912962963</v>
@@ -6346,13 +6354,13 @@
         <v>205</v>
       </c>
       <c r="B166" s="2">
-        <v>46007.35709490741</v>
+        <v>46007.68846064815</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D166" s="2">
-        <v>46007.57960648148</v>
+        <v>46007.94665509259</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>12</v>
@@ -6361,7 +6369,7 @@
         <v>201</v>
       </c>
       <c r="G166" s="2">
-        <v>24.8</v>
+        <v>19.65</v>
       </c>
       <c r="H166" s="2">
         <v>0</v>
@@ -6378,13 +6386,13 @@
         <v>206</v>
       </c>
       <c r="B167" s="2">
-        <v>46007.31993055555</v>
+        <v>46007.32144675926</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D167" s="2">
-        <v>46007.63166666667</v>
+        <v>46007.69633101852</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>12</v>
@@ -6393,7 +6401,7 @@
         <v>207</v>
       </c>
       <c r="G167" s="2">
-        <v>22.75</v>
+        <v>26.5</v>
       </c>
       <c r="H167" s="2">
         <v>0</v>
@@ -6410,13 +6418,13 @@
         <v>209</v>
       </c>
       <c r="B168" s="2">
-        <v>46007.32144675926</v>
+        <v>46007.37802083333</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D168" s="2">
-        <v>46007.69633101852</v>
+        <v>46007.52379629629</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>12</v>
@@ -6425,7 +6433,7 @@
         <v>207</v>
       </c>
       <c r="G168" s="2">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
@@ -6439,16 +6447,16 @@
     </row>
     <row r="169" spans="1:10">
       <c r="A169" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B169" s="2">
-        <v>46007.32284722223</v>
+        <v>46007.53501157407</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D169" s="2">
-        <v>46007.69303240741</v>
+        <v>46007.80540509259</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>12</v>
@@ -6457,7 +6465,7 @@
         <v>207</v>
       </c>
       <c r="G169" s="2">
-        <v>26.45</v>
+        <v>26.8</v>
       </c>
       <c r="H169" s="2">
         <v>0</v>
@@ -6471,16 +6479,16 @@
     </row>
     <row r="170" spans="1:10">
       <c r="A170" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B170" s="2">
-        <v>46007.53501157407</v>
+        <v>46007.31993055555</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D170" s="2">
-        <v>46007.80540509259</v>
+        <v>46007.63166666667</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>12</v>
@@ -6489,7 +6497,7 @@
         <v>207</v>
       </c>
       <c r="G170" s="2">
-        <v>26.8</v>
+        <v>22.75</v>
       </c>
       <c r="H170" s="2">
         <v>0</v>
@@ -6506,13 +6514,13 @@
         <v>211</v>
       </c>
       <c r="B171" s="2">
-        <v>46007.37802083333</v>
+        <v>46007.32284722223</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D171" s="2">
-        <v>46007.52379629629</v>
+        <v>46007.69303240741</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>12</v>
@@ -6521,7 +6529,7 @@
         <v>207</v>
       </c>
       <c r="G171" s="2">
-        <v>26.8</v>
+        <v>26.45</v>
       </c>
       <c r="H171" s="2">
         <v>0</v>
@@ -6570,13 +6578,13 @@
         <v>215</v>
       </c>
       <c r="B173" s="2">
-        <v>46007.3725462963</v>
+        <v>46007.35204861111</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D173" s="2">
-        <v>46007.65255787037</v>
+        <v>46007.6286574074</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>12</v>
@@ -6602,13 +6610,13 @@
         <v>216</v>
       </c>
       <c r="B174" s="2">
-        <v>46007.35204861111</v>
+        <v>46007.3725462963</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D174" s="2">
-        <v>46007.6286574074</v>
+        <v>46007.65255787037</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>12</v>
@@ -6759,16 +6767,16 @@
     </row>
     <row r="179" spans="1:10">
       <c r="A179" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B179" s="2">
-        <v>46007.3465162037</v>
+        <v>46007.31814814815</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D179" s="2">
-        <v>46007.52833333334</v>
+        <v>46007.71851851852</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>12</v>
@@ -6777,7 +6785,7 @@
         <v>225</v>
       </c>
       <c r="G179" s="2">
-        <v>26.75</v>
+        <v>23</v>
       </c>
       <c r="H179" s="2">
         <v>0</v>
@@ -6791,16 +6799,16 @@
     </row>
     <row r="180" spans="1:10">
       <c r="A180" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B180" s="2">
-        <v>46007.31814814815</v>
+        <v>46007.3465162037</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D180" s="2">
-        <v>46007.71851851852</v>
+        <v>46007.52833333334</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>12</v>
@@ -6809,7 +6817,7 @@
         <v>225</v>
       </c>
       <c r="G180" s="2">
-        <v>23</v>
+        <v>26.75</v>
       </c>
       <c r="H180" s="2">
         <v>0</v>
@@ -6850,71 +6858,71 @@
         <v>0</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="182" spans="1:10">
       <c r="A182" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B182" s="2">
+        <v>46007.49877314815</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D182" s="2">
+        <v>46007.72956018519</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F182" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B182" s="2">
-        <v>46007.31304398148</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D182" s="2">
-        <v>46007.73471064815</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F182" s="2" t="s">
+      <c r="G182" s="2">
+        <v>23</v>
+      </c>
+      <c r="H182" s="2">
+        <v>0</v>
+      </c>
+      <c r="I182" s="2">
+        <v>0</v>
+      </c>
+      <c r="J182" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="G182" s="2">
-        <v>23.35</v>
-      </c>
-      <c r="H182" s="2">
-        <v>0</v>
-      </c>
-      <c r="I182" s="2">
-        <v>0</v>
-      </c>
-      <c r="J182" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="183" spans="1:10">
       <c r="A183" s="2" t="s">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="B183" s="2">
-        <v>46007.49877314815</v>
+        <v>46007.31304398148</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D183" s="2">
-        <v>46007.72956018519</v>
+        <v>46007.73471064815</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F183" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G183" s="2">
+        <v>23.35</v>
+      </c>
+      <c r="H183" s="2">
+        <v>0</v>
+      </c>
+      <c r="I183" s="2">
+        <v>0</v>
+      </c>
+      <c r="J183" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="G183" s="2">
-        <v>23</v>
-      </c>
-      <c r="H183" s="2">
-        <v>0</v>
-      </c>
-      <c r="I183" s="2">
-        <v>0</v>
-      </c>
-      <c r="J183" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
   </sheetData>
